--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -142,7 +142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -152,17 +152,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.0</t>
+          <t xml:space="preserve">33.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">273.0</t>
+          <t xml:space="preserve">295.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMBINED-MERGE</t>
+          <t xml:space="preserve">ADJ-APPLIED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
+          <t xml:space="preserve">GRAHAM-1 [add_teacher] Graham Barber on [Cert III General (VOFF)] Thursday 9:00-2:30 (ICTCLD301): Graham Barber covers the Thursday VOFF (Cloud) session wks 10-13, before Anu takes over from wk14. Closes the wks 10-13 gap.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO-TEACHER</t>
+          <t xml:space="preserve">COMBINED-MERGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
+          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
+          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
+          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 9:00-2:30 Teaching: ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
+          <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 2:30-3:30 Tutorial Support: Tutorial Support</t>
+          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 9:00-2:30 Teaching: ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Thursday 9:00-2:30 Teaching: ICTPRG302 Apply introductory programming techniques.</t>
+          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 2:30-3:30 Tutorial Support: Tutorial Support</t>
         </is>
       </c>
     </row>
@@ -2649,6 +2649,18 @@
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Cert III General (F2F)] Thursday 9:00-2:30 Teaching: ICTPRG302 Apply introductory programming techniques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO-TEACHER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">[Cert III General (VOFF)] Tuesday 9:00-2:30 Teaching: BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.</t>
         </is>
@@ -2917,7 +2929,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
     </row>
@@ -3559,6 +3571,58 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00-2:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOFF</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anu Joshi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -1650,7 +1650,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jennie Agustin</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham Barber</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anu Joshi</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shanna Roper</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -68,7 +68,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -78,17 +78,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.5</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272.0</t>
+          <t xml:space="preserve">321.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -152,17 +152,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.5</t>
+          <t xml:space="preserve">40.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">295.0</t>
+          <t xml:space="preserve">368.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -179,27 +179,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">25.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">156.5</t>
+          <t xml:space="preserve">211.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -2351,134 +2351,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tuesday</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9:00-2:30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teaching</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tuesday</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2:30-3:30</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1-18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tutorial Support</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tutorial Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thursday</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9:00-2:30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9-18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teaching</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (VOFF)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tuesday</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9:00-2:30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teaching</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2506,7 +2378,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANU-1 [remove_teacher] Anu Joshi on [Cert III General (VOFF)] Thursday 9:00-2:30 (ICTNWK311): Anu teaches Thursday VOFF only from wk14; source listed her on the wks 1-9 networking session (with a duplicated 'Graham Barber') - removed.</t>
+          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026); Shaun Stummer continues wks 1-18. Prevents a clash with her Cert III VOFF Thursday unit (wks 14-18).</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2390,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026). Shaun Stummer continues wks 1-18.</t>
+          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
         </is>
       </c>
     </row>
@@ -2530,139 +2402,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANU-3 [add_teacher] Anu Joshi on [Cert III General (VOFF)] Thursday 9:00-2:30 (ICTCLD301): Anu takes the Thursday VOFF (Cloud) session from wk14 (15 Nov 2026). Wks 10-13 remain unassigned - flagged.</t>
+          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">COMBINED-MERGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
+          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">NO-TEACHER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
+          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">NO-TEACHER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRAHAM-1 [add_teacher] Graham Barber on [Cert III General (VOFF)] Thursday 9:00-2:30 (ICTCLD301): Graham Barber covers the Thursday VOFF (Cloud) session wks 10-13, before Anu takes over from wk14. Closes the wks 10-13 gap.</t>
+          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMBINED-MERGE</t>
+          <t xml:space="preserve">NO-TEACHER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 9:00-2:30 Teaching: ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 2:30-3:30 Tutorial Support: Tutorial Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Thursday 9:00-2:30 Teaching: ICTPRG302 Apply introductory programming techniques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (VOFF)] Tuesday 9:00-2:30 Teaching: BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.</t>
         </is>
       </c>
     </row>
@@ -2780,37 +2568,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00-3:30</t>
+          <t xml:space="preserve">9:00-2:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-8</t>
+          <t xml:space="preserve">10-18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.5</t>
+          <t xml:space="preserve">5.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">49.5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cert IV Programming</t>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">VOFF</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2820,12 +2608,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
+          <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun Stummer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2842,7 +2630,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-18</t>
+          <t xml:space="preserve">1-8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2852,7 +2640,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.0</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2872,7 +2660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
+          <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2884,37 +2672,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00-2:30</t>
+          <t xml:space="preserve">9:00-3:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-18</t>
+          <t xml:space="preserve">9-18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">6.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.5</t>
+          <t xml:space="preserve">65.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cert III General (VOFF)</t>
+          <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VOFF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2924,12 +2712,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.</t>
+          <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shaun Stummer</t>
         </is>
       </c>
     </row>
@@ -2941,45 +2729,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">9:00-2:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOFF</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTICT310 Identify and use industry specific technologies.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t xml:space="preserve">9:00-3:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">1-12</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">6.5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">78.0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teaching</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques | ICTPRG432 Develop data driven Apps | ICTPRG439 Use pre-existing components | ICTPRG430 Apply introductory object-oriented language skills | ICTPRG433 Test software developments</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -3371,22 +3211,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00-2:30</t>
+          <t xml:space="preserve">2:30-3:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-9</t>
+          <t xml:space="preserve">1-18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3401,12 +3241,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaching</t>
+          <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network</t>
+          <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3418,37 +3258,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:30-2:30</t>
+          <t xml:space="preserve">9:00-2:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-18</t>
+          <t xml:space="preserve">1-9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">5.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">49.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cert IV VOCF</t>
+          <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">F2F</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3458,7 +3298,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBINS405 Use integrated library management systems | BSBINS406 Assist customers to access information</t>
+          <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3470,27 +3310,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00-12:00</t>
+          <t xml:space="preserve">9:00-2:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-18</t>
+          <t xml:space="preserve">10-18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.0</t>
+          <t xml:space="preserve">5.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.0</t>
+          <t xml:space="preserve">49.5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3510,7 +3350,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to client.</t>
+          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3522,37 +3362,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00-2:30</t>
+          <t xml:space="preserve">12:30-2:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-9</t>
+          <t xml:space="preserve">1-18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cert III General (VOFF)</t>
+          <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VOFF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3562,7 +3402,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network.</t>
+          <t xml:space="preserve">BSBINS405 Use integrated library management systems | BSBINS406 Assist customers to access information</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3574,50 +3414,154 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00-12:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9-18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (F2F)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F2F</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to client.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Thursday</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">9:00-2:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">5.5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49.5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teaching</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00-2:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOFF</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3942,6 +3886,58 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00-2:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9-18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (F2F)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F2F</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -2373,24 +2373,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">SEMESTER-ASSUMED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026); Shaun Stummer continues wks 1-18. Prevents a clash with her Cert III VOFF Thursday unit (wks 14-18).</t>
+          <t xml:space="preserve">24 row(s) state no semester and were included in S2 2026: ICT30120 Cert III  General F2F OUR.docx (8); ICT30120 Cert III General VOF OUR.docx (8); ICT40120 Cert IV  Programming OUR.docx (8)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">SEMESTER-EXCLUDED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
+          <t xml:space="preserve">34 row(s) excluded as they state a different semester: S1 2027 (19); S1 2028 (6); S2 2027 (9)</t>
         </is>
       </c>
     </row>
@@ -2402,43 +2402,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
+          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026); Shaun Stummer continues wks 1-18. Prevents a clash with her Cert III VOFF Thursday unit (wks 14-18).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMBINED-MERGE</t>
+          <t xml:space="preserve">ADJ-APPLIED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
+          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO-TEACHER</t>
+          <t xml:space="preserve">ADJ-APPLIED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
+          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO-TEACHER</t>
+          <t xml:space="preserve">COMBINED-MERGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
+          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
         </is>
       </c>
     </row>
@@ -2449,6 +2449,30 @@
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO-TEACHER</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO-TEACHER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
         </is>

--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -2373,24 +2373,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEMESTER-ASSUMED</t>
+          <t xml:space="preserve">SEMESTER-EXCLUDED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 row(s) state no semester and were included in S2 2026: ICT30120 Cert III  General F2F OUR.docx (8); ICT30120 Cert III General VOF OUR.docx (8); ICT40120 Cert IV  Programming OUR.docx (8)</t>
+          <t xml:space="preserve">34 row(s) excluded as they state a different semester: S1 2027 (19); S1 2028 (6); S2 2027 (9)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEMESTER-EXCLUDED</t>
+          <t xml:space="preserve">ADJ-APPLIED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 row(s) excluded as they state a different semester: S1 2027 (19); S1 2028 (6); S2 2027 (9)</t>
+          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026); Shaun Stummer continues wks 1-18. Prevents a clash with her Cert III VOFF Thursday unit (wks 14-18).</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANU-2 [set_teacher_weeks] Anu Joshi on [Cert IV Programming] Thursday 9:00-3:30 (ICTPRG302): Anu stops the Thursday ICT40120 session after wk12 (8 Nov 2026); Shaun Stummer continues wks 1-18. Prevents a clash with her Cert III VOFF Thursday unit (wks 14-18).</t>
+          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
         </is>
       </c>
     </row>
@@ -2414,31 +2414,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-1 [set_teacher_weeks] Shanna Roper on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Shanna moves to the VOFF Wednesday session in wk9, so her F2F ICTWEB304 weeks become 1-8.</t>
+          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADJ-APPLIED</t>
+          <t xml:space="preserve">COMBINED-MERGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WED9-2 [add_teacher] Jennie Agustin on [Cert III General (F2F)] Wednesday 9:00-2:30 (ICTWEB304): Jennie Agustin takes the extra wk9 for F2F ICTWEB304 (Shanna is on VOFF).</t>
+          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMBINED-MERGE</t>
+          <t xml:space="preserve">NO-TEACHER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jennie Agustin Wednesday 2:30-3:30 tutorial: merged F2F+VOFF into one (Cert III General (F2F+VOFF combined)), counted once.</t>
+          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
+          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
         </is>
       </c>
     </row>
@@ -2461,18 +2461,6 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO-TEACHER</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
         </is>

--- a/output/teacher_timetables_S2_2026.xlsx
+++ b/output/teacher_timetables_S2_2026.xlsx
@@ -56,6 +56,26 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Load fraction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expected hrs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% of load</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Classes</t>
         </is>
       </c>
@@ -83,15 +103,35 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">33.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321.5</t>
+          <t xml:space="preserve">295.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163.9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVER</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (VOFF); Cert IV Programming</t>
         </is>
@@ -130,6 +170,26 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t xml:space="preserve">0.2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNDER</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Diploma Library Services - PTE Evening</t>
         </is>
       </c>
@@ -157,15 +217,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.0</t>
+          <t xml:space="preserve">38.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">368.0</t>
+          <t xml:space="preserve">352.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97.8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ON TRACK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F); Cert III General (VOFF); Cert IV Programming; Cert IV VOCF; Diploma Library Services - Fulltime VOFF</t>
         </is>
@@ -194,15 +274,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.5</t>
+          <t xml:space="preserve">23.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">211.5</t>
+          <t xml:space="preserve">198.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ON TRACK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F); Cert III General (F2F+VOFF combined); Cert III General (VOFF); Cert IV VOCF</t>
         </is>
@@ -241,6 +341,26 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t xml:space="preserve">0.3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVER</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
@@ -278,6 +398,26 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t xml:space="preserve">0.2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVER</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV VOCF; Diploma Library Services - Face to Face</t>
         </is>
       </c>
@@ -315,6 +455,26 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117.8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVER</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV VOCF; Diploma Library Services - Face to Face; Diploma Library Services - Fulltime VOFF; Diploma Library Services - PTE Evening</t>
         </is>
       </c>
@@ -352,6 +512,26 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t xml:space="preserve">0.2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNDER</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
@@ -379,15 +559,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.5</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">177.5</t>
+          <t xml:space="preserve">163.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90.6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ON TRACK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F); Cert III General (VOFF); Cert IV Programming</t>
         </is>
@@ -416,15 +616,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.5</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">351.0</t>
+          <t xml:space="preserve">324.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ON TRACK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
@@ -455,35 +675,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -512,30 +742,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS304 Process and maintain information resources</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -564,30 +804,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBWHS311 Assist with maintaining workplace safety</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -616,30 +866,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Face to Face</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS509 Promote literature and reading | BSBINS511 Develop and promote library activities, events and public programs</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -670,35 +930,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -727,30 +997,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Face to Face</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS505 Provide subject access and classify material</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -779,30 +1059,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Face to Face</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS516 Undertake cataloguing activities</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -831,30 +1121,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - PTE Evening</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">Evening</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS516 Undertake cataloguing activities | BSBINS505 Provide subject access and classify material</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -883,30 +1183,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS505 Provide subject access and classify material</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -935,30 +1245,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS516 Undertake cataloguing activities</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -987,30 +1307,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS305 Participate in cataloguing activities</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1039,30 +1369,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Time</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1091,30 +1431,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS508 Research and analyse information to meet library customer needs | BSBINS602 Extend own information literacy skills to locate information</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1143,30 +1493,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS509 Promote literature and reading | BSBINS511 Develop and promote library activities, events and public programs</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1195,30 +1555,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">28.0</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS407 Consolidate and maintain library industry knowledge</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1247,30 +1617,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">22.5</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS403 Obtain information from external and networked sources</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1299,30 +1679,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">22.5</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS404 Search library and information databases</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1353,35 +1743,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -1410,30 +1810,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">24.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBXCS404 Contribute to cyber security risk management. | ICTICT443 Work collaboratively in the ICT industry | ICTICT451 Comply with IP, ethics and privacy policies in ICT environments</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Graham Barber</t>
         </is>
@@ -1464,35 +1874,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -1521,30 +1941,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG440 Apply introductory programming skills in different languages | ICTWEB431 Create and style simple markup language</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -1573,30 +2003,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support | Shanna on Campus</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -1625,30 +2065,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTWEB304 Build Simple Web Pages.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1677,30 +2127,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1731,35 +2191,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -1788,30 +2258,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG440 Apply introductory programming skills in different languages | ICTWEB431 Create and style simple markup language</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Shanna Roper</t>
         </is>
@@ -1840,30 +2320,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG441 Apply skills in object-oriented design | ICTPRG444 Analyse software requirements</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1892,30 +2382,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support | Shanna on Campus</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Shanna Roper</t>
         </is>
@@ -1944,30 +2444,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Anu Joshi</t>
         </is>
@@ -1996,30 +2506,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Anu Joshi</t>
         </is>
@@ -2048,30 +2568,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">117.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques | ICTPRG432 Develop data driven Apps | ICTPRG439 Use pre-existing components | ICTPRG430 Apply introductory object-oriented language skills | ICTPRG433 Test software developments</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Anu Joshi</t>
         </is>
@@ -2216,6 +2746,78 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full-time load (hrs/semester)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break deducted when session &gt; 3 hrs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ON TRACK band</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90-110% of expected hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teachers ON TRACK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teachers UNDER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teachers OVER</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2433,12 +3035,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO-TEACHER</t>
+          <t xml:space="preserve">WORKLOAD-OFF-TRACK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
+          <t xml:space="preserve">Anu Joshi OVER (163.9% of load); Cathy Shay UNDER (75.0% of load); Judi Stievenard OVER (125.0% of load); Martina Clark OVER (125.0% of load); Narelle Bell OVER (117.8% of load); Rima Andrews UNDER (33.3% of load)</t>
         </is>
       </c>
     </row>
@@ -2450,7 +3052,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
+          <t xml:space="preserve">[Cert IV VOCF] Wednesday 3:30-5:00 Tutorial Support: Optional Tutorial support combined with Diploma Group</t>
         </is>
       </c>
     </row>
@@ -2461,6 +3063,18 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Cert IV VOCF] Thursday 12:30-2:30 Self-directed learning: Self-directed learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO-TEACHER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">[Diploma Library Services - Fulltime VOFF] Wednesday 3:30pm-5:00pm Tutorial Support: Tutorial time</t>
         </is>
@@ -2491,35 +3105,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -2548,30 +3172,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBXCS302 Identify and report online security threats. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environment</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2600,30 +3234,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2652,30 +3296,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -2704,30 +3358,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -2756,30 +3420,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTICT310 Identify and use industry specific technologies.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2808,30 +3482,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">78.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques | ICTPRG432 Develop data driven Apps | ICTPRG439 Use pre-existing components | ICTPRG430 Apply introductory object-oriented language skills | ICTPRG433 Test software developments</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer</t>
         </is>
@@ -2862,35 +3546,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -2919,30 +3613,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">54.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - PTE Evening</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">Evening</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS604 Contribute to collection management | BSBINS404 Search library and information databases</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2973,35 +3677,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -3030,30 +3744,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTSAS432 Identify and resolve client ICT problems</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3082,30 +3806,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">27.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Diploma Library Services - Fulltime VOFF</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS504 Maintain digital Repositories</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3134,30 +3868,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">24.0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBXCS404 Contribute to cyber security risk management. | ICTICT443 Work collaboratively in the ICT industry | ICTICT451 Comply with IP, ethics and privacy policies in ICT environments</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Rima Andrews</t>
         </is>
@@ -3186,30 +3930,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">30.0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV Programming</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBCRT404 Apply advanced critical thinking to work processes | ICTICT426 Identify and evaluate emerging technologies and practices | ICTSAS432 Identify and resolve client ICT problems</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3238,30 +3992,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3290,30 +4054,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3342,30 +4116,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3394,30 +4178,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">36.0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS405 Use integrated library management systems | BSBINS406 Assist customers to access information</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3446,30 +4240,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">30.0</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to client.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3498,30 +4302,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTNWK311 Install and test network protocols. | ICTSAS310 Install, configure and secure a small office or home office network.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3550,30 +4364,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3604,35 +4428,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -3661,30 +4495,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">45.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBXCS402 Promote workplace cyber security awareness and best practices (interspersed)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3713,30 +4557,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert III General (F2F+VOFF combined)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F/VOFF</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tutorial Support (combined online – AI focus)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3765,30 +4619,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTWEB304 Build Simple Web Pages.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3817,30 +4681,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">VOFF</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTWEB304 Build Simple Web Pages.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3869,30 +4743,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F/VOFF</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBXCS302 Identify and report online security threats. | ICTICT310 Identify and use industry specific technologies.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3921,30 +4805,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cert III General (F2F)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">F2F</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3975,35 +4869,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrs/session</t>
+          <t xml:space="preserve">Hrs (rostered)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact hrs (x weeks)</t>
+          <t xml:space="preserve">Break</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hrs/session (net)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact hrs (net x weeks)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Class</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Delivery</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Session type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Units / activity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Co-teacher(s)</t>
         </is>
@@ -4032,30 +4936,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">45.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBINS306 Provide multimedia support (interspersed)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4084,30 +4998,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBOPS404 Implement customer service strategies</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4136,30 +5060,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">25.0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBCRT411 Apply critical thinking to work practice</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4188,30 +5122,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">22.5</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">BSBPEF402 Develop personal work priorities</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4240,30 +5184,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">22.5</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Cert IV VOCF</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">CUAEVP411 Present information on activities, events or public program</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
